--- a/iter-v1.0.1-第二期/国内APP第二期测试分工.xlsx
+++ b/iter-v1.0.1-第二期/国内APP第二期测试分工.xlsx
@@ -166,7 +166,7 @@
     <t>总场数（仅展示）、活跃天数（仅展示）、单杆最高（点击进入单杆分页面）、我的视频数（点击进入我的视频页）</t>
   </si>
   <si>
-    <t>张梓聪</t>
+    <t>邹德乾</t>
   </si>
   <si>
     <t>7.2</t>
@@ -356,7 +356,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,13 +382,6 @@
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -895,148 +888,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
